--- a/employees/data/contract_1000.xlsx
+++ b/employees/data/contract_1000.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\جديد العقود\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="75" windowWidth="19440" windowHeight="7935"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14280" windowHeight="11868"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -19,12 +14,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">ورقة1!$C$1:$D$27</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
   <si>
     <t>علي كريم سلمان محمد</t>
   </si>
@@ -74,9 +69,6 @@
     <t>نور رحيم مكطوف</t>
   </si>
   <si>
-    <t>زيد فاظل حسن عبد</t>
-  </si>
-  <si>
     <t>زهراء علي محسن</t>
   </si>
   <si>
@@ -101,12 +93,6 @@
     <t>نور سعد عباس</t>
   </si>
   <si>
-    <t>الاسم</t>
-  </si>
-  <si>
-    <t>الراتب</t>
-  </si>
-  <si>
     <t>TBI</t>
   </si>
   <si>
@@ -116,15 +102,9 @@
     <t>الرافدين</t>
   </si>
   <si>
-    <t>المصرف</t>
-  </si>
-  <si>
     <t>دنيا محمد عباس علوان</t>
   </si>
   <si>
-    <t>الكود</t>
-  </si>
-  <si>
     <t>49A834</t>
   </si>
   <si>
@@ -134,9 +114,6 @@
     <t>C0D2B5</t>
   </si>
   <si>
-    <t>907916</t>
-  </si>
-  <si>
     <t>45CE5C</t>
   </si>
   <si>
@@ -164,6 +141,9 @@
     <t>8C200C</t>
   </si>
   <si>
+    <t>زيد فاضل حسن عبد</t>
+  </si>
+  <si>
     <t>CBE6E1</t>
   </si>
   <si>
@@ -201,12 +181,24 @@
   </si>
   <si>
     <t>B9C575</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>monthly_salary</t>
+  </si>
+  <si>
+    <t>bank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -357,7 +349,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -392,7 +384,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -602,32 +594,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.19921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
@@ -636,12 +628,12 @@
         <v>300000</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>4</v>
@@ -650,26 +642,26 @@
         <v>300000</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="7">
         <v>300000</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>907916</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
@@ -678,26 +670,26 @@
         <v>300000</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="7">
         <v>300000</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>12</v>
@@ -706,40 +698,40 @@
         <v>300000</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="7">
+        <v>300000</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="7">
-        <v>300000</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="C9" s="7">
         <v>300000</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>7</v>
@@ -748,12 +740,12 @@
         <v>300000</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>3</v>
@@ -762,26 +754,26 @@
         <v>300000</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="7">
         <v>300000</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>10</v>
@@ -790,26 +782,26 @@
         <v>300000</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C14" s="7">
         <v>300000</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>5</v>
@@ -818,12 +810,12 @@
         <v>300000</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
@@ -832,12 +824,12 @@
         <v>300000</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>11</v>
@@ -846,26 +838,26 @@
         <v>300000</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="7">
         <v>300000</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>2</v>
@@ -874,12 +866,12 @@
         <v>300000</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>14</v>
@@ -888,12 +880,12 @@
         <v>300000</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>0</v>
@@ -902,12 +894,12 @@
         <v>300000</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>13</v>
@@ -916,12 +908,12 @@
         <v>300000</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>1</v>
@@ -930,12 +922,12 @@
         <v>300000</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>15</v>
@@ -944,49 +936,49 @@
         <v>300000</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="7">
         <v>300000</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="7">
+        <v>300000</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="7">
-        <v>300000</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>20</v>
-      </c>
       <c r="C27" s="7">
         <v>300000</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +990,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1008,7 +1000,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
